--- a/output/Hunan/岳阳市_news.xlsx
+++ b/output/Hunan/岳阳市_news.xlsx
@@ -547,9 +547,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>False</t>
@@ -561,14 +559,12 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1576</v>
+        <v>1607</v>
       </c>
       <c r="M2" t="n">
         <v>2534</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=194</t>
@@ -617,9 +613,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>False</t>
@@ -631,14 +625,12 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>562</v>
+        <v>598</v>
       </c>
       <c r="M3" t="n">
         <v>441</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=195</t>
@@ -687,9 +679,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>False</t>
@@ -701,14 +691,12 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="M4" t="n">
         <v>141</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=197</t>
@@ -757,9 +745,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>False</t>
@@ -771,14 +757,12 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="M5" t="n">
         <v>968</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=200</t>
@@ -827,9 +811,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>False</t>
@@ -841,14 +823,12 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="M6" t="n">
         <v>83</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=201</t>
@@ -897,9 +877,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>False</t>
@@ -911,14 +889,12 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M7" t="n">
         <v>109</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=204</t>
@@ -967,9 +943,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>False</t>
@@ -981,14 +955,12 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="M8" t="n">
         <v>20</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=206</t>
@@ -1037,9 +1009,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>False</t>
@@ -1051,14 +1021,12 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M9" t="n">
         <v>45</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=207</t>
@@ -1107,9 +1075,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>False</t>
@@ -1121,14 +1087,12 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="M10" t="n">
         <v>41</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=210</t>
@@ -1177,9 +1141,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>False</t>
@@ -1191,14 +1153,12 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M11" t="n">
         <v>42</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=215</t>
@@ -1247,9 +1207,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>False</t>
@@ -1261,14 +1219,12 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M12" t="n">
         <v>42</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=216</t>
@@ -1321,9 +1277,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1335,14 +1289,12 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="M13" t="n">
         <v>39</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=211</t>
@@ -1395,9 +1347,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1409,14 +1359,12 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="M14" t="n">
         <v>40</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=192</t>
@@ -1469,9 +1417,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>False</t>
@@ -1483,14 +1429,12 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M15" t="n">
         <v>20</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=146</t>
@@ -1543,9 +1487,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1557,14 +1499,12 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="M16" t="n">
         <v>10</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=141</t>
@@ -1617,9 +1557,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>False</t>
@@ -1631,14 +1569,12 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="M17" t="n">
         <v>16</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=140</t>
@@ -1691,9 +1627,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>False</t>
@@ -1705,14 +1639,12 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M18" t="n">
         <v>10</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=139</t>
@@ -1765,9 +1697,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>True</t>
@@ -1779,14 +1709,12 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M19" t="n">
         <v>10</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=64</t>
@@ -1839,9 +1767,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>False</t>
@@ -1853,14 +1779,12 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="M20" t="n">
         <v>17</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=53</t>
@@ -1913,9 +1837,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>False</t>
@@ -1927,14 +1849,12 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=52</t>
@@ -1987,9 +1907,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>False</t>
@@ -2001,14 +1919,12 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M22" t="n">
         <v>12</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=51</t>
@@ -2061,9 +1977,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>False</t>
@@ -2075,14 +1989,12 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M23" t="n">
         <v>12</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=50</t>
@@ -2135,9 +2047,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>False</t>
@@ -2149,14 +2059,12 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="M24" t="n">
         <v>23</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=48</t>
@@ -2209,9 +2117,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>False</t>
@@ -2223,14 +2129,12 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="M25" t="n">
         <v>10</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=47</t>
@@ -2283,9 +2187,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>False</t>
@@ -2297,14 +2199,12 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="M26" t="n">
-        <v>20</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=46</t>
@@ -2357,9 +2257,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>False</t>
@@ -2371,14 +2269,12 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="M27" t="n">
         <v>20</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=45</t>
@@ -2431,9 +2327,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>False</t>
@@ -2445,14 +2339,12 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="M28" t="n">
         <v>31</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=44</t>
@@ -2505,9 +2397,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>False</t>
@@ -2519,14 +2409,12 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M29" t="n">
         <v>37</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=43</t>
@@ -2579,9 +2467,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>False</t>
@@ -2593,14 +2479,12 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>699</v>
+        <v>720</v>
       </c>
       <c r="M30" t="n">
         <v>551</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=15</t>
@@ -2649,9 +2533,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>False</t>
@@ -2663,14 +2545,12 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="M31" t="n">
         <v>833</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=193</t>
@@ -2719,9 +2599,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>False</t>
@@ -2733,14 +2611,12 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="M32" t="n">
         <v>323</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=196</t>
@@ -2789,9 +2665,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>False</t>
@@ -2803,14 +2677,12 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="M33" t="n">
-        <v>113</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=198</t>
@@ -2859,9 +2731,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>False</t>
@@ -2873,14 +2743,12 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="M34" t="n">
         <v>114</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=199</t>
@@ -2929,9 +2797,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>False</t>
@@ -2943,14 +2809,12 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="M35" t="n">
         <v>84</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=205</t>
@@ -2999,9 +2863,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>False</t>
@@ -3013,14 +2875,12 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="M36" t="n">
         <v>60</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=208</t>
@@ -3069,9 +2929,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3083,14 +2941,12 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="M37" t="n">
         <v>34</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=212</t>
@@ -3139,9 +2995,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>False</t>
@@ -3153,14 +3007,12 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M38" t="n">
         <v>39</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=213</t>
@@ -3209,9 +3061,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>False</t>
@@ -3223,14 +3073,12 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="M39" t="n">
         <v>40</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=214</t>
@@ -3279,9 +3127,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>False</t>
@@ -3293,14 +3139,12 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="M40" t="n">
         <v>41</v>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=203</t>
@@ -3353,9 +3197,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>False</t>
@@ -3367,14 +3209,12 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M41" t="n">
         <v>11</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=191</t>
@@ -3427,9 +3267,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>False</t>
@@ -3441,14 +3279,12 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="M42" t="n">
         <v>15</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=145</t>
@@ -3501,9 +3337,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>False</t>
@@ -3515,14 +3349,12 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="M43" t="n">
         <v>17</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=142</t>
@@ -3571,9 +3403,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>False</t>
@@ -3585,14 +3415,12 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=138</t>
@@ -3645,9 +3473,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>False</t>
@@ -3659,14 +3485,12 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>668</v>
+        <v>682</v>
       </c>
       <c r="M45" t="n">
         <v>110</v>
       </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=135</t>
@@ -3719,9 +3543,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>True</t>
@@ -3733,14 +3555,12 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="M46" t="n">
         <v>8</v>
       </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=109</t>
@@ -3789,9 +3609,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>False</t>
@@ -3803,14 +3621,12 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="M47" t="n">
         <v>11</v>
       </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=143</t>
@@ -3863,9 +3679,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>False</t>
@@ -3877,14 +3691,12 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M48" t="n">
-        <v>10</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=40</t>
@@ -3937,9 +3749,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>False</t>
@@ -3951,14 +3761,12 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="M49" t="n">
         <v>8</v>
       </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=136</t>
@@ -4011,9 +3819,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>False</t>
@@ -4025,14 +3831,12 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="M50" t="n">
         <v>9</v>
       </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=41</t>
@@ -4085,9 +3889,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>False</t>
@@ -4099,14 +3901,12 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="M51" t="n">
         <v>7</v>
       </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=137</t>
@@ -4159,9 +3959,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>False</t>
@@ -4173,14 +3971,12 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="M52" t="n">
         <v>101</v>
       </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=42</t>
@@ -4229,9 +4025,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>False</t>
@@ -4243,14 +4037,12 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="M53" t="n">
         <v>7</v>
       </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=153</t>
@@ -4299,9 +4091,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>False</t>
@@ -4313,14 +4103,12 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="M54" t="n">
         <v>16</v>
       </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=154</t>
@@ -4369,9 +4157,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>False</t>
@@ -4383,14 +4169,12 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="M55" t="n">
         <v>18</v>
       </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=155</t>
@@ -4439,9 +4223,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>False</t>
@@ -4453,14 +4235,12 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="M56" t="n">
         <v>19</v>
       </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=156</t>
@@ -4509,9 +4289,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>False</t>
@@ -4523,14 +4301,12 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="M57" t="n">
         <v>16</v>
       </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=157</t>
@@ -4579,9 +4355,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>False</t>
@@ -4593,14 +4367,12 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="M58" t="n">
         <v>50</v>
       </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=158</t>
@@ -4649,9 +4421,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>False</t>
@@ -4663,14 +4433,12 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="M59" t="n">
         <v>57</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=188</t>
@@ -4719,9 +4487,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>False</t>
@@ -4733,14 +4499,12 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="M60" t="n">
         <v>53</v>
       </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=152</t>
@@ -4789,9 +4553,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>False</t>
@@ -4803,14 +4565,12 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="M61" t="n">
         <v>46</v>
       </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=151</t>
@@ -4859,9 +4619,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>False</t>
@@ -4873,14 +4631,12 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M62" t="n">
         <v>48</v>
       </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=189</t>
@@ -4929,9 +4685,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>False</t>
@@ -4943,14 +4697,12 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="M63" t="n">
         <v>47</v>
       </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=150</t>
@@ -5003,9 +4755,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>True</t>
@@ -5017,14 +4767,12 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="M64" t="n">
         <v>11</v>
       </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=114</t>
@@ -5077,9 +4825,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>True</t>
@@ -5091,14 +4837,12 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M65" t="n">
         <v>17</v>
       </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=117</t>
@@ -5151,9 +4895,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>True</t>
@@ -5165,14 +4907,12 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="M66" t="n">
         <v>7</v>
       </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=120</t>
@@ -5225,9 +4965,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>True</t>
@@ -5239,14 +4977,12 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>5968</v>
+        <v>6072</v>
       </c>
       <c r="M67" t="n">
-        <v>17740</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
+        <v>17862</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=121</t>
@@ -5299,9 +5035,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>True</t>
@@ -5313,14 +5047,12 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="M68" t="n">
         <v>9</v>
       </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=122</t>
@@ -5373,9 +5105,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>True</t>
@@ -5387,14 +5117,12 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="M69" t="n">
         <v>10</v>
       </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=123</t>
@@ -5447,9 +5175,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>True</t>
@@ -5461,14 +5187,12 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="M70" t="n">
         <v>5</v>
       </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=124</t>
@@ -5521,9 +5245,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>True</t>
@@ -5535,14 +5257,12 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M71" t="n">
         <v>9</v>
       </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=125</t>
@@ -5595,9 +5315,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>True</t>
@@ -5609,14 +5327,12 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M72" t="n">
         <v>13</v>
       </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=126</t>
@@ -5669,9 +5385,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>True</t>
@@ -5683,14 +5397,12 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="M73" t="n">
         <v>11</v>
       </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=110</t>
@@ -5743,9 +5455,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>True</t>
@@ -5757,14 +5467,12 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M74" t="n">
         <v>8</v>
       </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=113</t>
@@ -5813,9 +5521,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>False</t>
@@ -5827,14 +5533,12 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M75" t="n">
         <v>15</v>
       </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=149</t>
@@ -5887,9 +5591,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>True</t>
@@ -5901,14 +5603,12 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M76" t="n">
         <v>9</v>
       </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=68</t>
@@ -5961,9 +5661,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>True</t>
@@ -5975,14 +5673,12 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="M77" t="n">
         <v>9</v>
       </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=71</t>
@@ -6035,9 +5731,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>True</t>
@@ -6049,14 +5743,12 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M78" t="n">
         <v>13</v>
       </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=72</t>
@@ -6109,9 +5801,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>True</t>
@@ -6123,14 +5813,12 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M79" t="n">
         <v>8</v>
       </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=73</t>
@@ -6183,9 +5871,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>False</t>
@@ -6197,14 +5883,12 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M80" t="n">
         <v>17</v>
       </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=132</t>
@@ -6253,9 +5937,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>False</t>
@@ -6267,14 +5949,12 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M81" t="n">
         <v>10</v>
       </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=190</t>
@@ -6327,9 +6007,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>True</t>
@@ -6341,14 +6019,12 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M82" t="n">
         <v>8</v>
       </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=128</t>
@@ -6401,9 +6077,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>False</t>
@@ -6415,14 +6089,12 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="M83" t="n">
         <v>17</v>
       </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=134</t>
@@ -6471,9 +6143,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>False</t>
@@ -6485,14 +6155,12 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="M84" t="n">
         <v>31</v>
       </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=187</t>
@@ -6541,9 +6209,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>False</t>
@@ -6555,14 +6221,12 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="M85" t="n">
         <v>28</v>
       </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=176</t>
@@ -6615,9 +6279,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>True</t>
@@ -6629,14 +6291,12 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="M86" t="n">
         <v>13</v>
       </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=115</t>
@@ -6689,9 +6349,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>True</t>
@@ -6703,14 +6361,12 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="M87" t="n">
         <v>10</v>
       </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=116</t>
@@ -6763,9 +6419,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>True</t>
@@ -6777,14 +6431,12 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="M88" t="n">
         <v>16</v>
       </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=119</t>
@@ -6833,9 +6485,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>False</t>
@@ -6847,14 +6497,12 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="M89" t="n">
         <v>17</v>
       </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=186</t>
@@ -6907,9 +6555,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>True</t>
@@ -6921,14 +6567,12 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="M90" t="n">
         <v>5</v>
       </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=66</t>
@@ -6977,9 +6621,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>False</t>
@@ -6991,14 +6633,12 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="M91" t="n">
         <v>12</v>
       </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=182</t>
@@ -7047,9 +6687,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>False</t>
@@ -7061,14 +6699,12 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="M92" t="n">
         <v>11</v>
       </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=177</t>
@@ -7117,9 +6753,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>False</t>
@@ -7131,14 +6765,12 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="M93" t="n">
         <v>16</v>
       </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=185</t>
@@ -7187,9 +6819,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>False</t>
@@ -7201,14 +6831,12 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="M94" t="n">
         <v>12</v>
       </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=178</t>
@@ -7257,9 +6885,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>False</t>
@@ -7271,14 +6897,12 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="M95" t="n">
         <v>9</v>
       </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=184</t>
@@ -7327,9 +6951,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>False</t>
@@ -7341,14 +6963,12 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="M96" t="n">
         <v>6</v>
       </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=179</t>
@@ -7397,9 +7017,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>False</t>
@@ -7411,14 +7029,12 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M97" t="n">
         <v>10</v>
       </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=183</t>
@@ -7467,9 +7083,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>False</t>
@@ -7481,14 +7095,12 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M98" t="n">
         <v>8</v>
       </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=180</t>
@@ -7537,9 +7149,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>False</t>
@@ -7551,14 +7161,12 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M99" t="n">
         <v>10</v>
       </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=181</t>
@@ -7607,9 +7215,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>False</t>
@@ -7621,14 +7227,12 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="M100" t="n">
         <v>35</v>
       </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=171</t>
@@ -7677,9 +7281,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>False</t>
@@ -7691,14 +7293,12 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M101" t="n">
         <v>28</v>
       </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=172</t>
@@ -7747,9 +7347,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>False</t>
@@ -7761,14 +7359,12 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="M102" t="n">
         <v>56</v>
       </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=163</t>
@@ -7817,9 +7413,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>False</t>
@@ -7831,14 +7425,12 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M103" t="n">
         <v>34</v>
       </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=173</t>
@@ -7891,9 +7483,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>False</t>
@@ -7905,14 +7495,12 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="M104" t="n">
         <v>33</v>
       </c>
-      <c r="N104" t="n">
-        <v>0</v>
-      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=39</t>
@@ -7961,9 +7549,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>False</t>
@@ -7975,14 +7561,12 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="M105" t="n">
         <v>10</v>
       </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=170</t>
@@ -8031,9 +7615,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>False</t>
@@ -8045,14 +7627,12 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="M106" t="n">
         <v>12</v>
       </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=164</t>
@@ -8101,9 +7681,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>False</t>
@@ -8115,14 +7693,12 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="M107" t="n">
         <v>9</v>
       </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=165</t>
@@ -8171,9 +7747,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>False</t>
@@ -8185,14 +7759,12 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="M108" t="n">
         <v>8</v>
       </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=166</t>
@@ -8241,9 +7813,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>False</t>
@@ -8255,14 +7825,12 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="M109" t="n">
         <v>8</v>
       </c>
-      <c r="N109" t="n">
-        <v>0</v>
-      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=167</t>
@@ -8311,9 +7879,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>False</t>
@@ -8325,14 +7891,12 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="M110" t="n">
         <v>10</v>
       </c>
-      <c r="N110" t="n">
-        <v>0</v>
-      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=168</t>
@@ -8381,9 +7945,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>False</t>
@@ -8395,14 +7957,12 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M111" t="n">
         <v>8</v>
       </c>
-      <c r="N111" t="n">
-        <v>0</v>
-      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=169</t>
@@ -8455,9 +8015,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>True</t>
@@ -8469,14 +8027,12 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M112" t="n">
         <v>7</v>
       </c>
-      <c r="N112" t="n">
-        <v>0</v>
-      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=100</t>
@@ -8529,9 +8085,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>True</t>
@@ -8543,14 +8097,12 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M113" t="n">
         <v>6</v>
       </c>
-      <c r="N113" t="n">
-        <v>0</v>
-      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=111</t>
@@ -8603,9 +8155,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>True</t>
@@ -8617,14 +8167,12 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M114" t="n">
         <v>14</v>
       </c>
-      <c r="N114" t="n">
-        <v>0</v>
-      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=95</t>
@@ -8677,9 +8225,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>True</t>
@@ -8691,14 +8237,12 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M115" t="n">
         <v>6</v>
       </c>
-      <c r="N115" t="n">
-        <v>0</v>
-      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=96</t>
@@ -8751,9 +8295,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>True</t>
@@ -8765,14 +8307,12 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="M116" t="n">
         <v>7</v>
       </c>
-      <c r="N116" t="n">
-        <v>0</v>
-      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=97</t>
@@ -8825,9 +8365,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>True</t>
@@ -8839,14 +8377,12 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="M117" t="n">
         <v>9</v>
       </c>
-      <c r="N117" t="n">
-        <v>0</v>
-      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=98</t>
@@ -8899,9 +8435,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>True</t>
@@ -8913,14 +8447,12 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="M118" t="n">
         <v>7</v>
       </c>
-      <c r="N118" t="n">
-        <v>0</v>
-      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=99</t>
@@ -8973,9 +8505,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>True</t>
@@ -8987,14 +8517,12 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="M119" t="n">
         <v>7</v>
       </c>
-      <c r="N119" t="n">
-        <v>0</v>
-      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=77</t>
@@ -9047,9 +8575,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>True</t>
@@ -9061,14 +8587,12 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="M120" t="n">
         <v>13</v>
       </c>
-      <c r="N120" t="n">
-        <v>0</v>
-      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=94</t>
@@ -9117,9 +8641,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>False</t>
@@ -9131,14 +8653,12 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="M121" t="n">
         <v>765</v>
       </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=175</t>
@@ -9187,9 +8707,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>False</t>
@@ -9201,14 +8719,12 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="M122" t="n">
-        <v>17</v>
-      </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=174</t>
@@ -9261,9 +8777,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>False</t>
@@ -9275,14 +8789,12 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="M123" t="n">
         <v>21</v>
       </c>
-      <c r="N123" t="n">
-        <v>0</v>
-      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=130</t>
@@ -9335,9 +8847,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>False</t>
@@ -9349,14 +8859,12 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="M124" t="n">
         <v>3340</v>
       </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=38</t>
@@ -9405,9 +8913,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>False</t>
@@ -9419,14 +8925,12 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="M125" t="n">
         <v>18</v>
       </c>
-      <c r="N125" t="n">
-        <v>0</v>
-      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=159</t>
@@ -9475,9 +8979,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>False</t>
@@ -9489,14 +8991,12 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M126" t="n">
         <v>14</v>
       </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=160</t>
@@ -9545,9 +9045,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>False</t>
@@ -9559,14 +9057,12 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M127" t="n">
         <v>7</v>
       </c>
-      <c r="N127" t="n">
-        <v>0</v>
-      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=161</t>
@@ -9615,9 +9111,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>False</t>
@@ -9629,14 +9123,12 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="M128" t="n">
         <v>6</v>
       </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=162</t>
@@ -9689,9 +9181,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>True</t>
@@ -9703,14 +9193,12 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="M129" t="n">
         <v>6</v>
       </c>
-      <c r="N129" t="n">
-        <v>0</v>
-      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=107</t>
@@ -9763,9 +9251,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>True</t>
@@ -9777,14 +9263,12 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="M130" t="n">
         <v>12</v>
       </c>
-      <c r="N130" t="n">
-        <v>0</v>
-      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=104</t>
@@ -9837,9 +9321,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I131" t="n">
-        <v>0</v>
-      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>True</t>
@@ -9851,14 +9333,12 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="M131" t="n">
         <v>8</v>
       </c>
-      <c r="N131" t="n">
-        <v>0</v>
-      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=105</t>
@@ -9911,9 +9391,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>True</t>
@@ -9925,14 +9403,12 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="M132" t="n">
         <v>7</v>
       </c>
-      <c r="N132" t="n">
-        <v>0</v>
-      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=106</t>
@@ -9985,9 +9461,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>True</t>
@@ -9999,14 +9473,12 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M133" t="n">
         <v>7</v>
       </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=101</t>
@@ -10059,9 +9531,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>True</t>
@@ -10073,14 +9543,12 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M134" t="n">
         <v>12</v>
       </c>
-      <c r="N134" t="n">
-        <v>0</v>
-      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=102</t>
@@ -10133,9 +9601,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>True</t>
@@ -10147,14 +9613,12 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M135" t="n">
         <v>9</v>
       </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=103</t>
@@ -10207,9 +9671,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>True</t>
@@ -10221,14 +9683,12 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M136" t="n">
         <v>9</v>
       </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=75</t>
@@ -10281,9 +9741,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I137" t="n">
-        <v>0</v>
-      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>True</t>
@@ -10295,14 +9753,12 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="M137" t="n">
         <v>10</v>
       </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=67</t>
@@ -10355,9 +9811,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>True</t>
@@ -10369,14 +9823,12 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="M138" t="n">
         <v>12</v>
       </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=69</t>
@@ -10429,9 +9881,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>True</t>
@@ -10443,14 +9893,12 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="M139" t="n">
         <v>10</v>
       </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=70</t>
@@ -10503,9 +9951,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>True</t>
@@ -10517,14 +9963,12 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>932</v>
+        <v>956</v>
       </c>
       <c r="M140" t="n">
         <v>298</v>
       </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=74</t>
@@ -10573,9 +10017,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>False</t>
@@ -10587,14 +10029,12 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="M141" t="n">
         <v>48</v>
       </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=202</t>
@@ -10647,9 +10087,7 @@
           <t>无条件共享</t>
         </is>
       </c>
-      <c r="I142" t="n">
-        <v>0</v>
-      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>False</t>
@@ -10661,14 +10099,12 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="M142" t="n">
         <v>37</v>
       </c>
-      <c r="N142" t="n">
-        <v>0</v>
-      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
           <t>https://www.yueyang.gov.cn/webapp/yydsj/dataDetail.jsp?id=209</t>
